--- a/Output/PowerPoint_Figures/Fig_S1/Fig_S1c_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_S1/Fig_S1c_data.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,120 +418,120 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="n">
+      <c r="B1" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" t="n">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>19</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>27</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>32</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>35</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" t="n">
         <v>38</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="Q1" t="n">
         <v>40</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="R1" t="n">
         <v>43</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" t="n">
         <v>45</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="T1" t="n">
         <v>48</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="U1" t="n">
         <v>51</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="V1" t="n">
         <v>53</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="W1" t="n">
         <v>56</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="X1" t="n">
         <v>59</v>
       </c>
-      <c r="Y1" s="1" t="n">
+      <c r="Y1" t="n">
         <v>61</v>
       </c>
-      <c r="Z1" s="1" t="n">
+      <c r="Z1" t="n">
         <v>64</v>
       </c>
-      <c r="AA1" s="1" t="n">
+      <c r="AA1" t="n">
         <v>66</v>
       </c>
-      <c r="AB1" s="1" t="n">
+      <c r="AB1" t="n">
         <v>69</v>
       </c>
-      <c r="AC1" s="1" t="n">
+      <c r="AC1" t="n">
         <v>72</v>
       </c>
-      <c r="AD1" s="1" t="n">
+      <c r="AD1" t="n">
         <v>74</v>
       </c>
-      <c r="AE1" s="1" t="n">
+      <c r="AE1" t="n">
         <v>77</v>
       </c>
-      <c r="AF1" s="1" t="n">
+      <c r="AF1" t="n">
         <v>80</v>
       </c>
-      <c r="AG1" s="1" t="n">
+      <c r="AG1" t="n">
         <v>82</v>
       </c>
-      <c r="AH1" s="1" t="n">
+      <c r="AH1" t="n">
         <v>85</v>
       </c>
-      <c r="AI1" s="1" t="n">
+      <c r="AI1" t="n">
         <v>88</v>
       </c>
-      <c r="AJ1" s="1" t="n">
+      <c r="AJ1" t="n">
         <v>90</v>
       </c>
-      <c r="AK1" s="1" t="n">
+      <c r="AK1" t="n">
         <v>93</v>
       </c>
-      <c r="AL1" s="1" t="n">
+      <c r="AL1" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -659,7 +647,7 @@
       <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -777,7 +765,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -895,7 +883,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -1013,7 +1001,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1131,14 +1119,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1.821360106895096</v>
+        <v>1.821360106895095</v>
       </c>
       <c r="D7" t="n">
         <v>1.960648903889771</v>
@@ -1245,7 +1233,7 @@
       <c r="AL7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -1302,7 +1290,7 @@
         <v>0.4358040117670267</v>
       </c>
       <c r="S8" t="n">
-        <v>2.505873067660404</v>
+        <v>2.505873067660403</v>
       </c>
       <c r="T8" t="n">
         <v>1.179234384781366</v>
@@ -1335,7 +1323,7 @@
         <v>0.2179020058835133</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.505873067660404</v>
+        <v>2.505873067660403</v>
       </c>
       <c r="AE8" t="n">
         <v>0.8352910225534678</v>
@@ -1361,7 +1349,7 @@
       <c r="AL8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -1394,7 +1382,7 @@
         <v>1.081491816385251</v>
       </c>
       <c r="K9" t="n">
-        <v>1.844897804422029</v>
+        <v>1.84489780442203</v>
       </c>
       <c r="L9" t="n">
         <v>1.145108982055053</v>
@@ -1479,7 +1467,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1593,7 +1581,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
@@ -1709,7 +1697,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
@@ -1721,10 +1709,10 @@
         <v>1.637007751999563</v>
       </c>
       <c r="D12" t="n">
-        <v>2.611982003190424</v>
+        <v>2.611982003190423</v>
       </c>
       <c r="E12" t="n">
-        <v>2.260629752761261</v>
+        <v>2.260629752761262</v>
       </c>
       <c r="F12" t="n">
         <v>0.9493946877268088</v>
@@ -1766,7 +1754,7 @@
         <v>2.611982003190609</v>
       </c>
       <c r="S12" t="n">
-        <v>1.893138216598236</v>
+        <v>1.893138216598235</v>
       </c>
       <c r="T12" t="n">
         <v>2.570078548593968</v>
@@ -1825,7 +1813,7 @@
       <c r="AL12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -1928,7 +1916,7 @@
         <v>0.2985074626865841</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.46268656716362</v>
+        <v>2.462686567163619</v>
       </c>
       <c r="AJ13" t="n">
         <v>0.3676470588234458</v>
@@ -1941,7 +1929,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>0.5.1</t>
         </is>
@@ -2037,7 +2025,7 @@
         <v>1.044776119403044</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.818181818181921</v>
+        <v>1.818181818181922</v>
       </c>
       <c r="AG14" t="n">
         <v>2.058823529411882</v>
@@ -2059,7 +2047,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>0.5.2</t>
         </is>
@@ -2173,11 +2161,11 @@
         <v>0.7352941176468917</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.46268656716362</v>
+        <v>2.462686567163619</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>0.5.3</t>
         </is>
@@ -2291,11 +2279,11 @@
         <v>1.885189437427815</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.46268656716362</v>
+        <v>2.462686567163619</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
@@ -2413,7 +2401,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>0.25.1</t>
         </is>
@@ -2524,14 +2512,14 @@
         <v>1.788211186113383</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.885245901638916</v>
+        <v>1.885245901638915</v>
       </c>
       <c r="AL18" t="n">
         <v>2.153846153845664</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>0.25.2</t>
         </is>
@@ -2576,7 +2564,7 @@
         <v>1.911764705882462</v>
       </c>
       <c r="O19" t="n">
-        <v>1.985294117646889</v>
+        <v>1.98529411764689</v>
       </c>
       <c r="P19" t="n">
         <v>1.014492753623246</v>
@@ -2649,7 +2637,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>0.125</t>
         </is>
@@ -2736,7 +2724,7 @@
         <v>1.343283582089629</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.391304347826224</v>
+        <v>2.391304347826223</v>
       </c>
       <c r="AD20" t="n">
         <v>2.246376811594331</v>
@@ -2767,7 +2755,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>0.125.1</t>
         </is>
@@ -2885,7 +2873,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>0.125.2</t>
         </is>
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>0.125.3</t>
         </is>
@@ -3121,7 +3109,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>0.062</t>
         </is>
@@ -3239,7 +3227,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>0.062.1</t>
         </is>
@@ -3269,7 +3257,7 @@
         <v>1.691176470588212</v>
       </c>
       <c r="J25" t="n">
-        <v>2.388059701492504</v>
+        <v>2.388059701492503</v>
       </c>
       <c r="K25" t="n">
         <v>1.641791044775979</v>
@@ -3335,7 +3323,7 @@
         <v>0.9701492537313984</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.391304347826224</v>
+        <v>2.391304347826223</v>
       </c>
       <c r="AG25" t="n">
         <v>1.8840579710146</v>
@@ -3357,7 +3345,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>0.062.2</t>
         </is>
@@ -3375,7 +3363,7 @@
         <v>1.029411764705868</v>
       </c>
       <c r="F26" t="n">
-        <v>2.388059701492504</v>
+        <v>2.388059701492503</v>
       </c>
       <c r="G26" t="n">
         <v>1.940298507462659</v>
@@ -3384,7 +3372,7 @@
         <v>0.4166666666666706</v>
       </c>
       <c r="I26" t="n">
-        <v>2.205882352941145</v>
+        <v>2.205882352941146</v>
       </c>
       <c r="J26" t="n">
         <v>1.343283582089533</v>
@@ -3475,7 +3463,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>0.062.3</t>
         </is>
@@ -3577,7 +3565,7 @@
         <v>0.6617647058823906</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.391304347826224</v>
+        <v>2.391304347826223</v>
       </c>
       <c r="AI27" t="n">
         <v>0.5882352941175133</v>
@@ -3589,7 +3577,7 @@
         <v>1.264266900789879</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.940298507462245</v>
+        <v>1.940298507462246</v>
       </c>
     </row>
   </sheetData>
@@ -3607,29 +3595,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Drug</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\Heatmaps\Vandetanib (G11)\Amp_dom_freq.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/Heatmaps/Vandetanib (G11)/Amp_dom_freq.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
